--- a/PDCA/PDCA-modelo.xlsx
+++ b/PDCA/PDCA-modelo.xlsx
@@ -317,7 +317,7 @@
     <t xml:space="preserve">Exemplo 2 - Compras</t>
   </si>
   <si>
-    <t xml:space="preserve">Ciclo preenchido em que a meta não foi atingida: reduzir o prazo de compra.</t>
+    <t xml:space="preserve">Ciclo preenchido em que a meta não foi atingida: reduzir o prazo de compra de uma distribuidora.</t>
   </si>
   <si>
     <t xml:space="preserve">Regras e premissas do modelo</t>
@@ -825,13 +825,13 @@
     <t xml:space="preserve">Líder da expedição</t>
   </si>
   <si>
-    <t xml:space="preserve">Causas confirmadas: a escala de entregadores é igual em todos os dias; os pedidos saem sem agrupamento por bairro; o formulário aceita endereço sem complemento.</t>
+    <t xml:space="preserve">Das doze hipóteses, cinco confirmadas. Seguem para o plano: a escala de entregadores igual em todos os dias; os pedidos sem agrupamento por bairro; o endereço sem complemento; a medição só pela média do dia. A fila do forno fica para o ciclo seguinte.</t>
   </si>
   <si>
     <t xml:space="preserve">Diagrama de Ishikawa; 5 porquês</t>
   </si>
   <si>
-    <t xml:space="preserve">Três ações: reforçar a escala no pico, agrupar pedidos por bairro na expedição e tornar o complemento do endereço obrigatório.</t>
+    <t xml:space="preserve">Seis ações: reforçar a escala no pico, tornar o complemento do endereço obrigatório, treinar a expedição, agrupar os pedidos por bairro, medir o tempo de entrega por faixa de horário e atualizar a instrução de trabalho.</t>
   </si>
   <si>
     <t xml:space="preserve">Plano de ação 5W2H</t>
@@ -918,7 +918,7 @@
     <t xml:space="preserve">Gerente de Suprimentos</t>
   </si>
   <si>
-    <t xml:space="preserve">Suprimentos</t>
+    <t xml:space="preserve">Distribuidora de materiais elétricos · Compras</t>
   </si>
   <si>
     <t xml:space="preserve">Equipe de compras</t>
@@ -1884,11 +1884,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="37175937"/>
-        <c:axId val="19572562"/>
+        <c:axId val="49306952"/>
+        <c:axId val="81622199"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="37175937"/>
+        <c:axId val="49306952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1920,7 +1920,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19572562"/>
+        <c:crossAx val="81622199"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1928,7 +1928,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19572562"/>
+        <c:axId val="81622199"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1967,7 +1967,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37175937"/>
+        <c:crossAx val="49306952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2356,11 +2356,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="71856809"/>
-        <c:axId val="23814726"/>
+        <c:axId val="26789668"/>
+        <c:axId val="13520487"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="71856809"/>
+        <c:axId val="26789668"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2392,7 +2392,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23814726"/>
+        <c:crossAx val="13520487"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2400,7 +2400,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23814726"/>
+        <c:axId val="13520487"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -2441,7 +2441,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71856809"/>
+        <c:crossAx val="26789668"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2836,11 +2836,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="9000566"/>
-        <c:axId val="22931790"/>
+        <c:axId val="44558870"/>
+        <c:axId val="2854335"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="9000566"/>
+        <c:axId val="44558870"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2872,7 +2872,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22931790"/>
+        <c:crossAx val="2854335"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2880,7 +2880,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="22931790"/>
+        <c:axId val="2854335"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="14"/>
@@ -2921,7 +2921,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9000566"/>
+        <c:crossAx val="44558870"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4098,12 +4098,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H5 H10 I15:I22" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="O indicador melhora quando sobe ou quando desce?" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D10" type="list">
       <formula1>"Maior é melhor,Menor é melhor"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H5 H10 I15:I22" type="date">
-      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Digite apenas o número, sem texto nem unidade." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D9" type="decimal">
@@ -4666,12 +4666,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
+    <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento, Concluída ou Cancelada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J6:J20" type="list">
+      <formula1>"Não iniciada,Em andamento,Concluída,Cancelada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G6:G20" type="date">
       <formula1>36526</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento, Concluída ou Cancelada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J6:J20" type="list">
-      <formula1>"Não iniciada,Em andamento,Concluída,Cancelada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Digite apenas o número, sem texto nem unidade." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I6:I20" type="decimal">
@@ -7124,12 +7124,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H5 H10 I15:I22" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="O indicador melhora quando sobe ou quando desce?" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D10" type="list">
       <formula1>"Maior é melhor,Menor é melhor"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H5 H10 I15:I22" type="date">
-      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Digite apenas o número, sem texto nem unidade." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D9" type="decimal">
@@ -7534,7 +7534,7 @@
         <v>265</v>
       </c>
       <c r="I19" s="58" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="J19" s="59" t="s">
         <v>100</v>
@@ -8310,12 +8310,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H5 H10 I15:I22" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="O indicador melhora quando sobe ou quando desce?" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D10" type="list">
       <formula1>"Maior é melhor,Menor é melhor"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H5 H10 I15:I22" type="date">
-      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Digite apenas o número, sem texto nem unidade." errorStyle="stop" errorTitle="Valor inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D9" type="decimal">
